--- a/data/valuebets_database_2025-09-15.xlsx
+++ b/data/valuebets_database_2025-09-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>16/09 15:30</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>175</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>16/09 16:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>150</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>16/09 16:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>150</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>16/09 15:30</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>150</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>16/09 17:45</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>140</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>16/09 17:45</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>140</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>16/09 16:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>140</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>16/09 17:45</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>125</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>17/09 15:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>140</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>16/09 17:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>140</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>16/09 16:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>125</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>16/09 15:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>125</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>17/09 15:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>125</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>16/09 17:45</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>110</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>16/09 17:45</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>110</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>16/09 17:45</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>110</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>16/09 15:30</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>110</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>16/09 17:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>110</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>16/09 17:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>110</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>17/09 15:30</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>110</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>17/09 15:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>110</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>17/09 16:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>100</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>16/09 17:45</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>95.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>95</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>21/09 13:30</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>60</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45915.07288481485</v>
+        <v>45915.07288481481</v>
       </c>
     </row>
     <row r="26">
@@ -1585,23 +1537,291 @@
           <t>16/09 17:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>100</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+48,6%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45915.07288481481</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Slovan Bra</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava – NitraExtraliga</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>16/09 16:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+121%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45915.13156815613</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Mhk 32 Lip</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Mhk 32 Liptovsky Mikulas – Spisska Nova VesExtraliga</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>16/09 16:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+106%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45915.13156815613</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | EHC Biel –</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EHC Biel – HC LuganoNational League A (ADJ98280) 385076e7</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>16/09 17:45</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+79,1%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45915.13156815613</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | SC Bern – </t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SC Bern – HC Ambri PiottaNational League A</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>16/09 17:45</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+78,6%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45915.13156815613</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betsson(FR)Hockey | Pas de buts | Severstal </t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Severstal Tcherepovets – Metallurg MagnitogorskRussie - KHL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>16/09 16:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+54,1%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45915.13156815613</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | Amur Khaba</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Amur Khabarovsk – Red Star KunlunRussie - KHL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>15/09 09:15</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>+48,6%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>45915.07288481485</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+53,4%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45915.13156815613</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-15.xlsx
+++ b/data/valuebets_database_2025-09-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>16/09 16:30</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>150</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45915.13156815613</v>
+        <v>45915.13156815972</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>16/09 16:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>140</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45915.13156815613</v>
+        <v>45915.13156815972</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>16/09 17:45</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>110</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45915.13156815613</v>
+        <v>45915.13156815972</v>
       </c>
     </row>
     <row r="30">
@@ -1715,10 +1709,8 @@
           <t>16/09 17:45</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>110</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1731,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45915.13156815613</v>
+        <v>45915.13156815972</v>
       </c>
     </row>
     <row r="31">
@@ -1760,10 +1752,8 @@
           <t>16/09 16:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>101</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1776,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45915.13156815613</v>
+        <v>45915.13156815972</v>
       </c>
     </row>
     <row r="32">
@@ -1805,23 +1795,156 @@
           <t>15/09 09:15</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="n">
+        <v>100</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+53,4%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45915.13156815972</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | MSHK Zilin</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MSHK Zilina – HC PresovExtraliga</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>16/09 15:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+149%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45915.18472746288</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Bili Tygri</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Bili Tygri Liberec – HC LitvinovExtraliga</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>16/09 16:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>+53,4%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>45915.13156815613</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+51,2%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45915.18472746288</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Leksands I</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Leksands IF – Örebro HKSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>16/09 17:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+49,7%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45915.18472746288</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-15.xlsx
+++ b/data/valuebets_database_2025-09-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,10 +1838,8 @@
           <t>16/09 15:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>175</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45915.18472746288</v>
+        <v>45915.18472746528</v>
       </c>
     </row>
     <row r="34">
@@ -1883,10 +1881,8 @@
           <t>16/09 16:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>100</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1899,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45915.18472746288</v>
+        <v>45915.18472746528</v>
       </c>
     </row>
     <row r="35">
@@ -1928,10 +1924,8 @@
           <t>16/09 17:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>100</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1944,7 +1938,52 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45915.18472746288</v>
+        <v>45915.18472746528</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey | Pas de buts | Leksands I</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Leksands IF – Orebro HKSuede - SHL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>16/09 17:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>95.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+52,9%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45915.22302549033</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-15.xlsx
+++ b/data/valuebets_database_2025-09-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,10 +1967,8 @@
           <t>16/09 17:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>95.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>95</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,367 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45915.22302549033</v>
+        <v>45915.22302548611</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Dukla Tren</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Dukla Trencin – HKM AS ZvolenExtraliga</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>16/09 16:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+115%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45915.27393489097</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Lausanne –</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Lausanne – Genève-ServetteNational League A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>16/09 17:45</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+82,1%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45915.27393489097</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Ceske Bude</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ceske Budejovice – HC PardubiceExtraliga</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>16/09 15:30</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+62,3%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45915.27393489097</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Liberec – </t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Liberec – LitvinovRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>16/09 16:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+60,6%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45915.27393489097</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey | Pas de buts | HC Ajoie –</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>HC Ajoie – RapperswilSuisse - NLA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>16/09 17:45</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+56,4%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45915.27393489097</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Linkopings</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Linkopings – Timra IKSHL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>16/09 17:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+55,0%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45915.27393489097</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Vaxjo Lake</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Vaxjo Lakers – HV 71SHL</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>16/09 17:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+54,3%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45915.27393489097</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey | Pas de buts | KalPa – Ki</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>KalPa – Kiekko-EspooFinlande - Liiga</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>16/09 15:30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>93.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+45,9%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45915.27393489097</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-15.xlsx
+++ b/data/valuebets_database_2025-09-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,10 +2010,8 @@
           <t>16/09 16:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>140</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45915.27393489097</v>
+        <v>45915.27393489583</v>
       </c>
     </row>
     <row r="38">
@@ -2055,10 +2053,8 @@
           <t>16/09 17:45</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>110</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2071,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45915.27393489097</v>
+        <v>45915.27393489583</v>
       </c>
     </row>
     <row r="39">
@@ -2100,10 +2096,8 @@
           <t>16/09 15:30</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>110</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2116,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45915.27393489097</v>
+        <v>45915.27393489583</v>
       </c>
     </row>
     <row r="40">
@@ -2145,10 +2139,8 @@
           <t>16/09 16:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>110</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2161,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45915.27393489097</v>
+        <v>45915.27393489583</v>
       </c>
     </row>
     <row r="41">
@@ -2190,10 +2182,8 @@
           <t>16/09 17:45</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>100</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2206,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45915.27393489097</v>
+        <v>45915.27393489583</v>
       </c>
     </row>
     <row r="42">
@@ -2235,10 +2225,8 @@
           <t>16/09 17:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>100</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2251,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45915.27393489097</v>
+        <v>45915.27393489583</v>
       </c>
     </row>
     <row r="43">
@@ -2280,10 +2268,8 @@
           <t>16/09 17:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>100</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2296,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45915.27393489097</v>
+        <v>45915.27393489583</v>
       </c>
     </row>
     <row r="44">
@@ -2325,10 +2311,8 @@
           <t>16/09 15:30</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>93.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>93</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2341,7 +2325,97 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45915.27393489097</v>
+        <v>45915.27393489583</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Banska Bys</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Banska Bystrica – HK PopradExtraliga</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>16/09 15:30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+122%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45915.30732086334</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Sparta Pra</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Sparta Prague – Energie Karlovy VaryExtraliga</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>16/09 16:30</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+84,3%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45915.30732086334</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-15.xlsx
+++ b/data/valuebets_database_2025-09-15.xlsx
@@ -2354,10 +2354,8 @@
           <t>16/09 15:30</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>150</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2370,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45915.30732086334</v>
+        <v>45915.30732086806</v>
       </c>
     </row>
     <row r="46">
@@ -2399,10 +2397,8 @@
           <t>16/09 16:30</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>125</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2415,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45915.30732086334</v>
+        <v>45915.30732086806</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-15.xlsx
+++ b/data/valuebets_database_2025-09-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2414,6 +2414,51 @@
         <v>45915.30732086806</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HC Kometa </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>HC Kometa Brno – HC VitkoviceExtraliga</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>16/09 16:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+52,0%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45915.39254940884</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-15.xlsx
+++ b/data/valuebets_database_2025-09-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,10 +2440,8 @@
           <t>16/09 16:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>100</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,52 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45915.39254940884</v>
+        <v>45915.39254940972</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | Admiral Vl</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Admiral Vladivostok – Red Star KunlunRussie - KHL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>17/09 09:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+52,4%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45915.43249775613</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-15.xlsx
+++ b/data/valuebets_database_2025-09-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2483,10 +2483,8 @@
           <t>17/09 09:30</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>101</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2499,7 +2497,52 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45915.43249775613</v>
+        <v>45915.43249775463</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Jukurit Mi</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Jukurit Mikkeli – Ilves TampereLiiga</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>17/09 15:30</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+67,7%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45915.47051278891</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-15.xlsx
+++ b/data/valuebets_database_2025-09-15.xlsx
@@ -2526,10 +2526,8 @@
           <t>17/09 15:30</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>110</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45915.47051278891</v>
+        <v>45915.47051278935</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-15.xlsx
+++ b/data/valuebets_database_2025-09-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2543,6 +2543,51 @@
         <v>45915.47051278935</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Vaasan Spo</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Vaasan Sport – Kärpät OuluLiiga - YYUZJR 385076e7</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>17/09 15:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+55,5%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45915.64087832178</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-15.xlsx
+++ b/data/valuebets_database_2025-09-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,10 +2569,8 @@
           <t>17/09 15:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>100</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,52 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45915.64087832178</v>
+        <v>45915.64087832176</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | AK Bars Ka</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AK Bars Kazan – Neftekhimik NijnekamskRussie - KHL - YYUZJR 385076e7</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>17/09 16:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+55,5%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45915.68552168522</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-15.xlsx
+++ b/data/valuebets_database_2025-09-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>17/09 16:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>101</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,97 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45915.68552168522</v>
+        <v>45915.68552168982</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Ajoie P</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HC Ajoie Porrentruy – SC Rapperswil-Jona LakersNational League A</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>16/09 17:45</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+96,1%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45915.72073573546</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | Jukurit Mi</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Jukurit Mikkeli – Ilves TampereFinlande - Liiga</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>17/09 15:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+51,8%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45915.72073573546</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-15.xlsx
+++ b/data/valuebets_database_2025-09-15.xlsx
@@ -2655,10 +2655,8 @@
           <t>16/09 17:45</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>125</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2671,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45915.72073573546</v>
+        <v>45915.72073574074</v>
       </c>
     </row>
     <row r="53">
@@ -2700,10 +2698,8 @@
           <t>17/09 15:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>100</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2716,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45915.72073573546</v>
+        <v>45915.72073574074</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-15.xlsx
+++ b/data/valuebets_database_2025-09-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2715,6 +2715,96 @@
         <v>45915.72073574074</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Brynas IF </t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Brynas IF – Lulea HFSHL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>16/09 17:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+57,5%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45915.80341055262</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Olomouc</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HC Olomouc – HC Rytiri KladnoExtraliga</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>17/09 16:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+56,1%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45915.80341055262</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-15.xlsx
+++ b/data/valuebets_database_2025-09-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2741,10 +2741,8 @@
           <t>16/09 17:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>100</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2757,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45915.80341055262</v>
+        <v>45915.80341055556</v>
       </c>
     </row>
     <row r="55">
@@ -2786,10 +2784,8 @@
           <t>17/09 16:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>100</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2802,7 +2798,52 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45915.80341055262</v>
+        <v>45915.80341055556</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Farjestads</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Farjestads BK – Malmo RedhawksSHL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>16/09 17:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+86,4%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45915.84895133036</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-15.xlsx
+++ b/data/valuebets_database_2025-09-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,10 +2827,8 @@
           <t>16/09 17:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>125</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,97 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45915.84895133036</v>
+        <v>45915.84895133102</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Dukla Mich</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Dukla Michalovce – HC KosiceExtraliga</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>16/09 15:30</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+73,6%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45915.88793680925</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | KalPa – Ki</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>KalPa – Kiekko-EspooLiiga</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>16/09 15:30</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+57,3%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45915.88793680925</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-15.xlsx
+++ b/data/valuebets_database_2025-09-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2870,10 +2870,8 @@
           <t>16/09 15:30</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>110</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45915.88793680925</v>
+        <v>45915.88793680556</v>
       </c>
     </row>
     <row r="58">
@@ -2915,10 +2913,8 @@
           <t>16/09 15:30</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>100</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,7 +2927,97 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45915.88793680925</v>
+        <v>45915.88793680556</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HIFK Helsi</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>HIFK Helsinki – Lukko RaumaLiiga</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>17/09 15:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+65,5%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45915.92990543308</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | America de</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>America de Cali – Atlético BucaramangaPrimera A</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>16/09 23:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+52,4%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45915.92990543308</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-15.xlsx
+++ b/data/valuebets_database_2025-09-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2956,10 +2956,8 @@
           <t>17/09 15:30</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>110</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2972,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45915.92990543308</v>
+        <v>45915.92990542824</v>
       </c>
     </row>
     <row r="60">
@@ -3001,10 +2999,8 @@
           <t>16/09 23:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>60</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3017,7 +3013,322 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45915.92990543308</v>
+        <v>45915.92990542824</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | EHC Munich</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>EHC Munich – AugsbourgDEL</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>19/09 17:30</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+182%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45915.97117994518</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Iserlohn R</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Iserlohn Roosters – Nurnberg Ice TigersAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>19/09 17:30</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+164%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45915.97117994518</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Löwen Fran</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Löwen Frankfurt – DresdnerAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>18/09 17:30</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+164%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45915.97117994518</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Adler Mann</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Adler Mannheim – BerlinDEL</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>19/09 17:30</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+156%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45915.97117994518</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ingolstadt</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ingolstadt – Wolfsburg GrizzlyAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>19/09 17:30</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+129%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45915.97117994518</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Schwenning</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Schwenninger Wild Wings – Kölner HaieAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>19/09 17:30</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+127%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45915.97117994518</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Fischtown </t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Fischtown Pinguins – Straubing TigersAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>19/09 17:30</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+67,2%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45915.97117994518</v>
       </c>
     </row>
   </sheetData>
